--- a/data/trans_orig/P6706-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P6706-Estudios-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo requiere que esconda sus emociones en 2012</t>
+          <t>Población según si su trabajo requiere que esconda sus emociones en 2012 (tasa de respuesta: 98,51%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>35212</t>
+          <t>34202</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>59266</t>
+          <t>58439</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>32,8%</t>
+          <t>32,34%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>27258</t>
+          <t>28078</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>49763</t>
+          <t>49017</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>36,1%</t>
+          <t>35,56%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>68838</t>
+          <t>68466</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>101662</t>
+          <t>100937</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>21,49%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>31,91%</t>
+          <t>31,69%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17341</t>
+          <t>17529</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>35994</t>
+          <t>37126</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14550</t>
+          <t>13680</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>31538</t>
+          <t>31745</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>36143</t>
+          <t>35633</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>60423</t>
+          <t>60493</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>18,99%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>25054</t>
+          <t>25635</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>46370</t>
+          <t>47864</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>26,49%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>21543</t>
+          <t>21614</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>41131</t>
+          <t>40370</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>29,84%</t>
+          <t>29,29%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>52013</t>
+          <t>52638</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>80379</t>
+          <t>81220</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>25,23%</t>
+          <t>25,5%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21662</t>
+          <t>21393</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>43063</t>
+          <t>42864</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>23,72%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2922</t>
+          <t>2163</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13748</t>
+          <t>12781</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>26011</t>
+          <t>27592</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>50143</t>
+          <t>50830</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>15,96%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>32512</t>
+          <t>30995</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>54837</t>
+          <t>53969</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>30,34%</t>
+          <t>29,86%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>31240</t>
+          <t>31141</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>52239</t>
+          <t>53562</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>37,9%</t>
+          <t>38,86%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>69258</t>
+          <t>67811</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>100364</t>
+          <t>101611</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>31,5%</t>
+          <t>31,9%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>153976</t>
+          <t>159297</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>206744</t>
+          <t>207749</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>69063</t>
+          <t>69552</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>104581</t>
+          <t>105489</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>238139</t>
+          <t>239307</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>300660</t>
+          <t>299519</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>20,3%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>80827</t>
+          <t>78186</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>119071</t>
+          <t>114422</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>63316</t>
+          <t>62323</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>96660</t>
+          <t>95095</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>152594</t>
+          <t>153693</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>203254</t>
+          <t>204081</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,83%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>168336</t>
+          <t>168648</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>220284</t>
+          <t>217311</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>23,96%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>92515</t>
+          <t>91533</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>131714</t>
+          <t>130546</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>23,16%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>270855</t>
+          <t>271923</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>335746</t>
+          <t>336735</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>22,82%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>166273</t>
+          <t>166339</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>215947</t>
+          <t>215603</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>23,77%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>110493</t>
+          <t>110684</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>150884</t>
+          <t>150611</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>26,49%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>288345</t>
+          <t>287588</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>353411</t>
+          <t>350863</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,49%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>23,78%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>214091</t>
+          <t>214079</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>272187</t>
+          <t>271687</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>30,01%</t>
+          <t>29,96%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>141618</t>
+          <t>142279</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>186805</t>
+          <t>184927</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>32,85%</t>
+          <t>32,52%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>375483</t>
+          <t>374028</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>447482</t>
+          <t>444694</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>30,32%</t>
+          <t>30,14%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>19542</t>
+          <t>19299</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>41669</t>
+          <t>40641</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>20074</t>
+          <t>20286</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>42070</t>
+          <t>42272</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>45482</t>
+          <t>45114</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>76053</t>
+          <t>76304</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>13,95%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>25662</t>
+          <t>26293</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>51435</t>
+          <t>51644</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5914</t>
+          <t>6001</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>19682</t>
+          <t>19878</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>35621</t>
+          <t>36390</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>65560</t>
+          <t>65126</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>11,91%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>39181</t>
+          <t>39549</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>67506</t>
+          <t>66542</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>42096</t>
+          <t>40396</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>69275</t>
+          <t>68680</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>29,9%</t>
+          <t>29,64%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>86480</t>
+          <t>87097</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>125499</t>
+          <t>125273</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>22,9%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>59670</t>
+          <t>60197</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>92420</t>
+          <t>93096</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>29,52%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>27902</t>
+          <t>29087</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>53113</t>
+          <t>54468</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>23,51%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>96261</t>
+          <t>95847</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>137514</t>
+          <t>135186</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>24,71%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>102582</t>
+          <t>104283</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>141061</t>
+          <t>139844</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>32,53%</t>
+          <t>33,07%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>44,73%</t>
+          <t>44,35%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>78019</t>
+          <t>79335</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>112384</t>
+          <t>110467</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>33,67%</t>
+          <t>34,24%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>48,51%</t>
+          <t>47,68%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>193848</t>
+          <t>193900</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>240808</t>
+          <t>244358</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>35,44%</t>
+          <t>35,45%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>44,02%</t>
+          <t>44,67%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>226888</t>
+          <t>227178</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>287693</t>
+          <t>290132</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>20,68%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>133043</t>
+          <t>130260</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>179893</t>
+          <t>177708</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>375269</t>
+          <t>374109</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>447936</t>
+          <t>447937</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,7 +2863,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>137127</t>
+          <t>135570</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>186982</t>
+          <t>186864</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,47 +2906,47 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
+          <t>9,66%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>13,32%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>111852</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>91650</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>133910</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>11,92%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
           <t>9,77%</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>13,33%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>111852</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>93111</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>134150</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>11,92%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>9,92%</t>
-        </is>
-      </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>241027</t>
+          <t>244132</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>306827</t>
+          <t>305431</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>13,05%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>252599</t>
+          <t>251740</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>315933</t>
+          <t>315952</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,7 +3019,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>172400</t>
+          <t>170147</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>222969</t>
+          <t>221835</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>23,64%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>440220</t>
+          <t>437780</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>520183</t>
+          <t>520810</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>22,25%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>266144</t>
+          <t>268570</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>327802</t>
+          <t>331958</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>152128</t>
+          <t>154388</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>200915</t>
+          <t>203309</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>434935</t>
+          <t>432426</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>516493</t>
+          <t>518054</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>22,13%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>373751</t>
+          <t>375507</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>445379</t>
+          <t>444731</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>26,64%</t>
+          <t>26,76%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>31,7%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>270509</t>
+          <t>271220</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>330925</t>
+          <t>328008</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>28,83%</t>
+          <t>28,91%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>35,27%</t>
+          <t>34,96%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>667375</t>
+          <t>664750</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>755642</t>
+          <t>752467</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>28,39%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>32,28%</t>
+          <t>32,14%</t>
         </is>
       </c>
     </row>
@@ -3496,7 +3496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo requiere que esconda sus emociones en 2016</t>
+          <t>Población según si su trabajo requiere que esconda sus emociones en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3691,12 +3691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>28220</t>
+          <t>28152</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>50871</t>
+          <t>50337</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3706,12 +3706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>35,54%</t>
+          <t>35,17%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9473</t>
+          <t>9576</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>22921</t>
+          <t>24108</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3741,12 +3741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,8%</t>
+          <t>33,44%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>41438</t>
+          <t>41124</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>67104</t>
+          <t>66826</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>31,18%</t>
+          <t>31,05%</t>
         </is>
       </c>
     </row>
@@ -3804,12 +3804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20300</t>
+          <t>20125</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>40237</t>
+          <t>39996</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3819,12 +3819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>27,95%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10652</t>
+          <t>10244</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>24939</t>
+          <t>25311</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3854,12 +3854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>34,6%</t>
+          <t>35,11%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>34343</t>
+          <t>33451</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>59030</t>
+          <t>58404</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>27,14%</t>
         </is>
       </c>
     </row>
@@ -3917,12 +3917,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>23225</t>
+          <t>22532</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>42827</t>
+          <t>43079</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3932,12 +3932,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>29,92%</t>
+          <t>30,1%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>8835</t>
+          <t>9004</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>22228</t>
+          <t>22333</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3967,12 +3967,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>30,84%</t>
+          <t>30,98%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>35149</t>
+          <t>35467</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>60158</t>
+          <t>59870</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>27,95%</t>
+          <t>27,82%</t>
         </is>
       </c>
     </row>
@@ -4030,12 +4030,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15862</t>
+          <t>15622</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>34707</t>
+          <t>34472</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4045,12 +4045,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4065,12 +4065,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7769</t>
+          <t>7804</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20213</t>
+          <t>20935</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,04%</t>
+          <t>29,04%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4100,12 +4100,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>26828</t>
+          <t>26398</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>50233</t>
+          <t>48899</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4115,12 +4115,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>22,72%</t>
         </is>
       </c>
     </row>
@@ -4143,12 +4143,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>11787</t>
+          <t>12115</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>29871</t>
+          <t>31305</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4158,12 +4158,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4178,12 +4178,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>6493</t>
+          <t>6624</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>18958</t>
+          <t>18624</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4193,12 +4193,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>26,3%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4213,12 +4213,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>22319</t>
+          <t>21798</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>44129</t>
+          <t>43627</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>20,27%</t>
         </is>
       </c>
     </row>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>175759</t>
+          <t>178025</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>228256</t>
+          <t>227157</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4388,12 +4388,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>81113</t>
+          <t>80120</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>115588</t>
+          <t>115567</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4423,12 +4423,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>271045</t>
+          <t>271620</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>333011</t>
+          <t>332943</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4458,7 +4458,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>129135</t>
+          <t>126899</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>172481</t>
+          <t>173665</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>80311</t>
+          <t>80873</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>116935</t>
+          <t>116913</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4536,7 +4536,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>219179</t>
+          <t>221414</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>278250</t>
+          <t>276200</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,5%</t>
         </is>
       </c>
     </row>
@@ -4599,12 +4599,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>174952</t>
+          <t>176135</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>226079</t>
+          <t>227917</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>138396</t>
+          <t>142414</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>184531</t>
+          <t>186980</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>28,27%</t>
+          <t>28,64%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>329855</t>
+          <t>331026</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>393811</t>
+          <t>396940</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>25,16%</t>
         </is>
       </c>
     </row>
@@ -4712,12 +4712,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>178958</t>
+          <t>178818</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>228269</t>
+          <t>229913</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>24,85%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4747,12 +4747,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>104202</t>
+          <t>104562</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>144840</t>
+          <t>143885</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>22,04%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>294163</t>
+          <t>294889</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>355800</t>
+          <t>357641</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>22,66%</t>
         </is>
       </c>
     </row>
@@ -4825,12 +4825,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>148304</t>
+          <t>148833</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>194364</t>
+          <t>196470</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4840,12 +4840,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>21,24%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4860,12 +4860,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>150184</t>
+          <t>149715</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>195975</t>
+          <t>195194</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>22,94%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>29,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>308444</t>
+          <t>308867</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>375718</t>
+          <t>375907</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>23,82%</t>
         </is>
       </c>
     </row>
@@ -5055,12 +5055,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>48767</t>
+          <t>47952</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>79007</t>
+          <t>79355</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5070,12 +5070,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>22,53%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5090,12 +5090,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>37087</t>
+          <t>38126</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>63164</t>
+          <t>63333</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>20,53%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>94183</t>
+          <t>93128</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>134612</t>
+          <t>132453</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>20,1%</t>
         </is>
       </c>
     </row>
@@ -5168,12 +5168,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>38497</t>
+          <t>38141</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>65869</t>
+          <t>64639</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5203,12 +5203,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>27351</t>
+          <t>27003</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>51477</t>
+          <t>49937</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5238,12 +5238,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>72644</t>
+          <t>71892</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>106177</t>
+          <t>106045</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>16,09%</t>
         </is>
       </c>
     </row>
@@ -5281,12 +5281,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>58285</t>
+          <t>57234</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>90049</t>
+          <t>91724</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5296,12 +5296,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>26,16%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>52819</t>
+          <t>52045</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>81763</t>
+          <t>81700</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>26,49%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>119000</t>
+          <t>118546</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>162811</t>
+          <t>161907</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>24,57%</t>
         </is>
       </c>
     </row>
@@ -5394,12 +5394,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>57386</t>
+          <t>57714</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>90752</t>
+          <t>91427</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5409,12 +5409,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>26,08%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5429,12 +5429,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>46063</t>
+          <t>43998</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>73464</t>
+          <t>74012</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5444,12 +5444,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5464,12 +5464,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>110958</t>
+          <t>112651</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>153880</t>
+          <t>153870</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5479,7 +5479,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -5507,12 +5507,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>75808</t>
+          <t>75411</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>107880</t>
+          <t>110276</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5522,12 +5522,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>30,77%</t>
+          <t>31,45%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>79594</t>
+          <t>81957</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>113112</t>
+          <t>114477</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>26,57%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>36,67%</t>
+          <t>37,11%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>166232</t>
+          <t>166944</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>213242</t>
+          <t>215140</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>32,36%</t>
+          <t>32,64%</t>
         </is>
       </c>
     </row>
@@ -5737,12 +5737,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>273878</t>
+          <t>271981</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>335353</t>
+          <t>335768</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5752,12 +5752,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>139363</t>
+          <t>138920</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>184544</t>
+          <t>188296</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>428008</t>
+          <t>428080</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>505328</t>
+          <t>505792</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>20,63%</t>
         </is>
       </c>
     </row>
@@ -5850,12 +5850,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>202477</t>
+          <t>200993</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>259966</t>
+          <t>259384</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5865,12 +5865,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>132366</t>
+          <t>132689</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>177620</t>
+          <t>177698</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>345877</t>
+          <t>349191</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>420708</t>
+          <t>421286</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>17,18%</t>
         </is>
       </c>
     </row>
@@ -5963,12 +5963,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>275874</t>
+          <t>274673</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>338450</t>
+          <t>336325</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>19,36%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>23,7%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>215339</t>
+          <t>217034</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>270801</t>
+          <t>268990</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>21,0%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>26,03%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>507558</t>
+          <t>508527</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>591868</t>
+          <t>590328</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>20,74%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>24,07%</t>
         </is>
       </c>
     </row>
@@ -6076,12 +6076,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>267636</t>
+          <t>266703</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>328589</t>
+          <t>330106</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6091,12 +6091,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>23,16%</t>
+          <t>23,26%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>169634</t>
+          <t>172459</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>219615</t>
+          <t>221308</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>455014</t>
+          <t>453413</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>535885</t>
+          <t>536455</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>18,49%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>21,88%</t>
         </is>
       </c>
     </row>
@@ -6189,12 +6189,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>252405</t>
+          <t>252804</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>312976</t>
+          <t>316363</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6204,12 +6204,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>22,3%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>251026</t>
+          <t>252903</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>311104</t>
+          <t>310949</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6239,12 +6239,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>30,11%</t>
+          <t>30,09%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>519518</t>
+          <t>523162</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>605731</t>
+          <t>607922</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6274,12 +6274,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>21,33%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>24,79%</t>
         </is>
       </c>
     </row>
@@ -6455,7 +6455,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo requiere que esconda sus emociones en 2023</t>
+          <t>Población según si su trabajo requiere que esconda sus emociones en 2023 (tasa de respuesta: 99,45%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6650,12 +6650,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8393</t>
+          <t>8004</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20229</t>
+          <t>20700</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6665,12 +6665,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>25,48%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>61,41%</t>
+          <t>62,84%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6685,12 +6685,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3521</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9925</t>
+          <t>9669</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>54,53%</t>
+          <t>53,12%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13459</t>
+          <t>14241</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>27035</t>
+          <t>28499</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>26,31%</t>
+          <t>27,84%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>52,86%</t>
+          <t>55,72%</t>
         </is>
       </c>
     </row>
@@ -6763,12 +6763,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1529</t>
+          <t>1320</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11143</t>
+          <t>10288</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6778,12 +6778,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>33,83%</t>
+          <t>31,23%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6798,12 +6798,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>356</t>
+          <t>354</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5215</t>
+          <t>5367</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6813,12 +6813,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>28,65%</t>
+          <t>29,48%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6833,12 +6833,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2792</t>
+          <t>2611</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>13059</t>
+          <t>12136</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6848,12 +6848,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>23,73%</t>
         </is>
       </c>
     </row>
@@ -6876,12 +6876,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2003</t>
+          <t>2437</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12837</t>
+          <t>13922</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6891,12 +6891,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>38,97%</t>
+          <t>42,26%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6911,12 +6911,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2929</t>
+          <t>2776</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9012</t>
+          <t>9262</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6926,12 +6926,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>49,51%</t>
+          <t>50,88%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>6667</t>
+          <t>6863</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>18745</t>
+          <t>19301</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6961,12 +6961,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>36,65%</t>
+          <t>37,74%</t>
         </is>
       </c>
     </row>
@@ -6989,12 +6989,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>764</t>
+          <t>714</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7205</t>
+          <t>7296</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7004,12 +7004,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7024,12 +7024,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1229</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6390</t>
+          <t>6367</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7039,12 +7039,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>35,1%</t>
+          <t>34,98%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3086</t>
+          <t>2922</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>11489</t>
+          <t>10744</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7074,12 +7074,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>21,01%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1888</t>
+          <t>1992</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>12540</t>
+          <t>12388</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>38,07%</t>
+          <t>37,61%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7142,7 +7142,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3805</t>
+          <t>3752</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7157,7 +7157,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>20,61%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2659</t>
+          <t>2506</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>14412</t>
+          <t>13092</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>28,18%</t>
+          <t>25,6%</t>
         </is>
       </c>
     </row>
@@ -7332,12 +7332,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>30659</t>
+          <t>25345</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>181862</t>
+          <t>183282</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7347,12 +7347,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>35,61%</t>
+          <t>35,89%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>36386</t>
+          <t>35868</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>56606</t>
+          <t>57146</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7382,12 +7382,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>24,89%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>53670</t>
+          <t>57074</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>215364</t>
+          <t>215513</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7417,12 +7417,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>29,09%</t>
+          <t>29,11%</t>
         </is>
       </c>
     </row>
@@ -7445,12 +7445,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>17515</t>
+          <t>13798</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>116340</t>
+          <t>116184</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>22,75%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>28925</t>
+          <t>29528</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>48093</t>
+          <t>49205</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7495,47 +7495,47 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
+          <t>12,86%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>21,43%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>93284</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>42895</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>149736</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
           <t>12,6%</t>
         </is>
       </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>20,95%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>93284</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>37296</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>147946</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>12,6%</t>
-        </is>
-      </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>20,23%</t>
         </is>
       </c>
     </row>
@@ -7558,12 +7558,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>18287</t>
+          <t>18540</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>126662</t>
+          <t>125756</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7593,12 +7593,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>50714</t>
+          <t>49638</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>74120</t>
+          <t>74198</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7608,12 +7608,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>32,29%</t>
+          <t>32,32%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>52878</t>
+          <t>51718</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>191683</t>
+          <t>191646</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7643,12 +7643,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>25,89%</t>
         </is>
       </c>
     </row>
@@ -7671,12 +7671,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>59335</t>
+          <t>57061</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>423603</t>
+          <t>443611</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7686,12 +7686,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>82,95%</t>
+          <t>86,87%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7706,12 +7706,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>25835</t>
+          <t>25993</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>45482</t>
+          <t>46105</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7721,12 +7721,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7741,12 +7741,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>94005</t>
+          <t>96561</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>563347</t>
+          <t>550167</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7756,12 +7756,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>76,1%</t>
+          <t>74,32%</t>
         </is>
       </c>
     </row>
@@ -7784,12 +7784,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5934</t>
+          <t>6258</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>57756</t>
+          <t>57613</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7799,12 +7799,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7819,12 +7819,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>38421</t>
+          <t>38158</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>60630</t>
+          <t>60826</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7834,12 +7834,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>16,62%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>26,41%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7854,12 +7854,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>28845</t>
+          <t>30865</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>122483</t>
+          <t>119896</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7869,12 +7869,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,2%</t>
         </is>
       </c>
     </row>
@@ -8014,12 +8014,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>25361</t>
+          <t>25026</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>48761</t>
+          <t>48063</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8029,12 +8029,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>38,94%</t>
+          <t>38,38%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>19626</t>
+          <t>19652</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>36842</t>
+          <t>37201</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8064,12 +8064,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>34,86%</t>
+          <t>35,19%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>51422</t>
+          <t>50626</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>80040</t>
+          <t>79525</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>21,92%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>34,66%</t>
+          <t>34,44%</t>
         </is>
       </c>
     </row>
@@ -8127,12 +8127,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8477</t>
+          <t>8704</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>24776</t>
+          <t>23850</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8142,12 +8142,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8162,12 +8162,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8370</t>
+          <t>8650</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>21422</t>
+          <t>21610</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8177,12 +8177,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,44%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8197,12 +8197,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>19931</t>
+          <t>20366</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>39474</t>
+          <t>39137</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8212,12 +8212,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>16,95%</t>
         </is>
       </c>
     </row>
@@ -8240,12 +8240,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>20291</t>
+          <t>20414</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>40366</t>
+          <t>41484</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8255,12 +8255,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>32,24%</t>
+          <t>33,13%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8275,12 +8275,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>20254</t>
+          <t>19780</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>36219</t>
+          <t>36107</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8290,12 +8290,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>34,27%</t>
+          <t>34,16%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8310,12 +8310,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>45497</t>
+          <t>45483</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>71709</t>
+          <t>69899</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8330,7 +8330,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>31,05%</t>
+          <t>30,27%</t>
         </is>
       </c>
     </row>
@@ -8353,12 +8353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7053</t>
+          <t>7532</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>21703</t>
+          <t>21117</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8388,12 +8388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>9583</t>
+          <t>9211</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>23276</t>
+          <t>23241</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8403,12 +8403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>21,99%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>20214</t>
+          <t>20546</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>40234</t>
+          <t>39280</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8438,12 +8438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>17,01%</t>
         </is>
       </c>
     </row>
@@ -8466,12 +8466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>20677</t>
+          <t>20501</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>44114</t>
+          <t>44222</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8481,12 +8481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>35,23%</t>
+          <t>35,32%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8501,12 +8501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>14799</t>
+          <t>14577</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>29655</t>
+          <t>29120</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8516,12 +8516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>27,55%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>38801</t>
+          <t>39207</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>66787</t>
+          <t>66586</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>28,92%</t>
+          <t>28,84%</t>
         </is>
       </c>
     </row>
@@ -8696,12 +8696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>55301</t>
+          <t>51538</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>231298</t>
+          <t>229422</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8711,12 +8711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>34,58%</t>
+          <t>34,3%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>66440</t>
+          <t>66391</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>95209</t>
+          <t>94081</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8746,12 +8746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>26,62%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>102854</t>
+          <t>107022</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>300703</t>
+          <t>296113</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8781,12 +8781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>29,41%</t>
+          <t>28,97%</t>
         </is>
       </c>
     </row>
@@ -8809,12 +8809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>26518</t>
+          <t>28837</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>123837</t>
+          <t>127138</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8824,12 +8824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>42912</t>
+          <t>43678</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>66354</t>
+          <t>65782</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8859,12 +8859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>18,61%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>66599</t>
+          <t>58070</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>177766</t>
+          <t>177732</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8894,7 +8894,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -8922,12 +8922,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>34703</t>
+          <t>39196</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>159482</t>
+          <t>160825</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8937,12 +8937,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8957,12 +8957,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>81194</t>
+          <t>82032</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>109223</t>
+          <t>111495</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8972,12 +8972,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>30,9%</t>
+          <t>31,54%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8992,12 +8992,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>99409</t>
+          <t>89824</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>263298</t>
+          <t>260980</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9007,12 +9007,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>25,53%</t>
         </is>
       </c>
     </row>
@@ -9035,12 +9035,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>74708</t>
+          <t>73058</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>515248</t>
+          <t>521088</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9050,12 +9050,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>77,04%</t>
+          <t>77,91%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9070,12 +9070,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>43145</t>
+          <t>42565</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>66086</t>
+          <t>66363</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9085,12 +9085,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9105,12 +9105,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>129157</t>
+          <t>131892</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>668140</t>
+          <t>702591</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>65,36%</t>
+          <t>68,73%</t>
         </is>
       </c>
     </row>
@@ -9148,12 +9148,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>22317</t>
+          <t>22321</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>109342</t>
+          <t>106199</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9168,7 +9168,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9183,12 +9183,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>58221</t>
+          <t>58433</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>85876</t>
+          <t>85632</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9198,12 +9198,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>24,23%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9218,12 +9218,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>68711</t>
+          <t>64167</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>183645</t>
+          <t>182902</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>17,89%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P6706-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P6706-Estudios-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>34202</t>
+          <t>34532</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>58439</t>
+          <t>57608</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>32,34%</t>
+          <t>31,88%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>28078</t>
+          <t>27588</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>49017</t>
+          <t>48688</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>35,56%</t>
+          <t>35,32%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>68466</t>
+          <t>68270</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>100937</t>
+          <t>99975</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>31,69%</t>
+          <t>31,38%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17529</t>
+          <t>17747</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>37126</t>
+          <t>37276</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>20,63%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13680</t>
+          <t>13822</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>31745</t>
+          <t>31005</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>35633</t>
+          <t>36760</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>60493</t>
+          <t>60558</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>19,01%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>25635</t>
+          <t>25668</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>47864</t>
+          <t>47323</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>26,19%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>21614</t>
+          <t>20967</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>40370</t>
+          <t>41619</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>30,19%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>52638</t>
+          <t>51756</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>81220</t>
+          <t>81083</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>25,45%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21393</t>
+          <t>21915</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>42864</t>
+          <t>43363</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2163</t>
+          <t>2217</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12781</t>
+          <t>12909</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>27592</t>
+          <t>26553</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>50830</t>
+          <t>51368</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>16,12%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>30995</t>
+          <t>32450</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>53969</t>
+          <t>54384</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>29,86%</t>
+          <t>30,09%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>31141</t>
+          <t>30980</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>53562</t>
+          <t>53062</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>22,47%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>38,86%</t>
+          <t>38,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>67811</t>
+          <t>68513</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>101611</t>
+          <t>100309</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>31,9%</t>
+          <t>31,49%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>159297</t>
+          <t>159283</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>207749</t>
+          <t>209436</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>23,09%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>69552</t>
+          <t>71635</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>105489</t>
+          <t>106835</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>239307</t>
+          <t>238857</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>299519</t>
+          <t>297792</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>20,18%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>78186</t>
+          <t>80700</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>114422</t>
+          <t>117807</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>62323</t>
+          <t>61575</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>95095</t>
+          <t>95449</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>153693</t>
+          <t>151314</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>204081</t>
+          <t>200878</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>13,61%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>168648</t>
+          <t>168638</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>217311</t>
+          <t>219534</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>91533</t>
+          <t>92245</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>130546</t>
+          <t>132088</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>271923</t>
+          <t>274387</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>336735</t>
+          <t>337113</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>22,85%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>166339</t>
+          <t>167795</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>215603</t>
+          <t>220545</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>110684</t>
+          <t>109521</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>150611</t>
+          <t>151840</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>287588</t>
+          <t>289240</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>350863</t>
+          <t>356153</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>24,14%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>214079</t>
+          <t>217108</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>271687</t>
+          <t>274029</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>29,96%</t>
+          <t>30,21%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>142279</t>
+          <t>142930</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>184927</t>
+          <t>184549</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>25,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>32,52%</t>
+          <t>32,45%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>374028</t>
+          <t>376485</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>444694</t>
+          <t>448265</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>25,51%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>30,14%</t>
+          <t>30,38%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>19299</t>
+          <t>20135</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>40641</t>
+          <t>43872</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>20286</t>
+          <t>19610</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>42272</t>
+          <t>43035</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>45114</t>
+          <t>45362</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>76304</t>
+          <t>75870</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>13,87%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>26293</t>
+          <t>25490</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>51644</t>
+          <t>52027</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6001</t>
+          <t>6792</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>19878</t>
+          <t>20485</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>36390</t>
+          <t>36075</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>65126</t>
+          <t>65408</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>11,96%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>39549</t>
+          <t>39436</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>66542</t>
+          <t>66313</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>40396</t>
+          <t>41737</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>68680</t>
+          <t>69920</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>29,64%</t>
+          <t>30,18%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>87097</t>
+          <t>88533</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>125273</t>
+          <t>127603</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>23,33%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>60197</t>
+          <t>60349</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>93096</t>
+          <t>93200</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>29,52%</t>
+          <t>29,56%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>29087</t>
+          <t>27781</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>54468</t>
+          <t>52815</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
+          <t>22,8%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>95847</t>
+          <t>95191</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>135186</t>
+          <t>139161</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>25,44%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>104283</t>
+          <t>104114</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>139844</t>
+          <t>140132</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>33,07%</t>
+          <t>33,02%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>44,35%</t>
+          <t>44,44%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>79335</t>
+          <t>79124</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>110467</t>
+          <t>111506</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>34,24%</t>
+          <t>34,15%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>47,68%</t>
+          <t>48,13%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>193900</t>
+          <t>191596</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>244358</t>
+          <t>240622</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>35,45%</t>
+          <t>35,02%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>44,67%</t>
+          <t>43,99%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>227178</t>
+          <t>227262</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>290132</t>
+          <t>285452</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>130260</t>
+          <t>130678</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>177708</t>
+          <t>178145</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>374109</t>
+          <t>371453</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>447937</t>
+          <t>451330</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>19,28%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>135570</t>
+          <t>138712</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>186864</t>
+          <t>188008</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>91650</t>
+          <t>92977</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>133910</t>
+          <t>134966</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>244132</t>
+          <t>239686</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>305431</t>
+          <t>303795</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>12,98%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>251740</t>
+          <t>251869</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>315952</t>
+          <t>316035</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>170147</t>
+          <t>170648</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>221835</t>
+          <t>224494</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>18,19%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>437780</t>
+          <t>435127</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>520810</t>
+          <t>515029</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>22,0%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>268570</t>
+          <t>265734</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>331958</t>
+          <t>328549</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>154388</t>
+          <t>153712</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>203309</t>
+          <t>204678</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>432426</t>
+          <t>433640</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>518054</t>
+          <t>512336</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>21,88%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>375507</t>
+          <t>374345</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>444731</t>
+          <t>443885</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>26,68%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>31,7%</t>
+          <t>31,64%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>271220</t>
+          <t>267076</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>328008</t>
+          <t>330489</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>28,47%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>34,96%</t>
+          <t>35,23%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>664750</t>
+          <t>666817</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>752467</t>
+          <t>760282</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>28,39%</t>
+          <t>28,48%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>32,14%</t>
+          <t>32,47%</t>
         </is>
       </c>
     </row>
@@ -3691,12 +3691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>28152</t>
+          <t>26931</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>50337</t>
+          <t>49764</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3706,12 +3706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>35,17%</t>
+          <t>34,77%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9576</t>
+          <t>9161</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24108</t>
+          <t>22989</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3741,12 +3741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>33,44%</t>
+          <t>31,89%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>41124</t>
+          <t>40984</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>66826</t>
+          <t>67001</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>31,05%</t>
+          <t>31,13%</t>
         </is>
       </c>
     </row>
@@ -3804,12 +3804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20125</t>
+          <t>18704</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>39996</t>
+          <t>38433</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3819,12 +3819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>27,95%</t>
+          <t>26,85%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10244</t>
+          <t>10287</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>25311</t>
+          <t>24896</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3854,12 +3854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>35,11%</t>
+          <t>34,54%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>33451</t>
+          <t>33653</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>58404</t>
+          <t>59433</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>27,14%</t>
+          <t>27,62%</t>
         </is>
       </c>
     </row>
@@ -3917,12 +3917,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>22532</t>
+          <t>22601</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>43079</t>
+          <t>43970</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3932,12 +3932,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>30,1%</t>
+          <t>30,72%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>9004</t>
+          <t>9047</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>22333</t>
+          <t>22748</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3967,12 +3967,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>30,98%</t>
+          <t>31,56%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>35467</t>
+          <t>36125</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>59870</t>
+          <t>60251</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>28,0%</t>
         </is>
       </c>
     </row>
@@ -4030,12 +4030,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15622</t>
+          <t>16097</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>34472</t>
+          <t>34158</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4045,12 +4045,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>23,87%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4065,12 +4065,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7804</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20935</t>
+          <t>19830</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>29,04%</t>
+          <t>27,51%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4100,12 +4100,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>26398</t>
+          <t>26570</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>48899</t>
+          <t>48836</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4115,12 +4115,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>22,69%</t>
         </is>
       </c>
     </row>
@@ -4143,12 +4143,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>12115</t>
+          <t>12699</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>31305</t>
+          <t>29746</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4158,12 +4158,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4178,12 +4178,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>6624</t>
+          <t>6781</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>18624</t>
+          <t>18717</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4193,12 +4193,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>25,96%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4213,12 +4213,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>21798</t>
+          <t>21806</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>43627</t>
+          <t>44173</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4233,7 +4233,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,53%</t>
         </is>
       </c>
     </row>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>178025</t>
+          <t>176602</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>227157</t>
+          <t>229992</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4388,12 +4388,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>24,86%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>80120</t>
+          <t>78710</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>115567</t>
+          <t>117111</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4423,12 +4423,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>271620</t>
+          <t>273041</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>332943</t>
+          <t>332238</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>21,05%</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>126899</t>
+          <t>127756</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>173665</t>
+          <t>173020</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>80873</t>
+          <t>81079</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>116913</t>
+          <t>118820</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4536,12 +4536,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>221414</t>
+          <t>219960</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>276200</t>
+          <t>279040</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>17,68%</t>
         </is>
       </c>
     </row>
@@ -4599,12 +4599,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>176135</t>
+          <t>176398</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>227917</t>
+          <t>227491</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>24,59%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>142414</t>
+          <t>140276</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>186980</t>
+          <t>186509</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>21,49%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>28,57%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>331026</t>
+          <t>331009</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>396940</t>
+          <t>395688</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4689,7 +4689,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>25,08%</t>
         </is>
       </c>
     </row>
@@ -4712,12 +4712,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>178818</t>
+          <t>176490</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>229913</t>
+          <t>226293</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>24,46%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4747,12 +4747,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>104562</t>
+          <t>103610</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>143885</t>
+          <t>144215</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>294889</t>
+          <t>291950</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>357641</t>
+          <t>355057</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>22,5%</t>
         </is>
       </c>
     </row>
@@ -4825,12 +4825,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>148833</t>
+          <t>147069</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>196470</t>
+          <t>196058</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4840,12 +4840,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4860,12 +4860,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>149715</t>
+          <t>151707</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>195194</t>
+          <t>195223</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>29,9%</t>
+          <t>29,91%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>308867</t>
+          <t>311479</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>375907</t>
+          <t>378962</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>19,74%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>24,02%</t>
         </is>
       </c>
     </row>
@@ -5055,12 +5055,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>47952</t>
+          <t>49009</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>79355</t>
+          <t>79827</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5070,12 +5070,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5090,12 +5090,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>38126</t>
+          <t>37592</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>63333</t>
+          <t>63518</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>20,59%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>93128</t>
+          <t>92498</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>132453</t>
+          <t>133547</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>20,26%</t>
         </is>
       </c>
     </row>
@@ -5168,12 +5168,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>38141</t>
+          <t>38051</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>64639</t>
+          <t>65613</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5203,12 +5203,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>27003</t>
+          <t>27645</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>49937</t>
+          <t>49806</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5238,12 +5238,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>71892</t>
+          <t>70907</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>106045</t>
+          <t>108191</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>16,42%</t>
         </is>
       </c>
     </row>
@@ -5281,12 +5281,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>57234</t>
+          <t>57729</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>91724</t>
+          <t>90001</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5296,12 +5296,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>25,67%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>52045</t>
+          <t>51454</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>81700</t>
+          <t>80230</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>26,01%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>118546</t>
+          <t>119011</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>161907</t>
+          <t>161243</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>24,47%</t>
         </is>
       </c>
     </row>
@@ -5394,12 +5394,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>57714</t>
+          <t>58262</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>91427</t>
+          <t>90363</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5409,12 +5409,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,62%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5429,12 +5429,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>43998</t>
+          <t>45855</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>74012</t>
+          <t>73841</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5444,12 +5444,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5464,12 +5464,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>112651</t>
+          <t>112449</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>153870</t>
+          <t>155722</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5479,12 +5479,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>23,63%</t>
         </is>
       </c>
     </row>
@@ -5507,12 +5507,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>75411</t>
+          <t>74332</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>110276</t>
+          <t>107942</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5522,12 +5522,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>31,45%</t>
+          <t>30,79%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>81957</t>
+          <t>81187</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>114477</t>
+          <t>114126</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>26,32%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>37,11%</t>
+          <t>37,0%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>166944</t>
+          <t>163442</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>215140</t>
+          <t>210625</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>25,33%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>32,64%</t>
+          <t>31,96%</t>
         </is>
       </c>
     </row>
@@ -5737,12 +5737,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>271981</t>
+          <t>275863</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>335768</t>
+          <t>336101</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5752,12 +5752,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>23,69%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>138920</t>
+          <t>139842</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>188296</t>
+          <t>188228</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5787,7 +5787,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>428080</t>
+          <t>426999</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>505792</t>
+          <t>504438</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>20,57%</t>
         </is>
       </c>
     </row>
@@ -5850,12 +5850,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>200993</t>
+          <t>199281</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>259384</t>
+          <t>255097</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5865,12 +5865,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>132689</t>
+          <t>131585</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>177698</t>
+          <t>176074</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>349191</t>
+          <t>346360</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>421286</t>
+          <t>419313</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>17,1%</t>
         </is>
       </c>
     </row>
@@ -5963,12 +5963,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>274673</t>
+          <t>275485</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>336325</t>
+          <t>337385</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>23,78%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>217034</t>
+          <t>216849</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>268990</t>
+          <t>270940</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>26,22%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>508527</t>
+          <t>511062</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>590328</t>
+          <t>591006</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>24,1%</t>
         </is>
       </c>
     </row>
@@ -6076,12 +6076,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>266703</t>
+          <t>267689</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>330106</t>
+          <t>329353</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6091,12 +6091,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>18,87%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>172459</t>
+          <t>169845</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>221308</t>
+          <t>221186</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>453413</t>
+          <t>452847</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>536455</t>
+          <t>532300</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>21,71%</t>
         </is>
       </c>
     </row>
@@ -6189,12 +6189,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>252804</t>
+          <t>252370</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>316363</t>
+          <t>314407</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6204,12 +6204,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>252903</t>
+          <t>252688</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>310949</t>
+          <t>310210</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6239,12 +6239,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>24,45%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>30,02%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>523162</t>
+          <t>516863</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>607922</t>
+          <t>606704</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6274,12 +6274,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>24,74%</t>
         </is>
       </c>
     </row>
@@ -6645,32 +6645,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>14099</t>
+          <t>20375</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8004</t>
+          <t>11842</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20700</t>
+          <t>28062</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>42,8%</t>
+          <t>49,18%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>28,58%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>62,84%</t>
+          <t>67,73%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6680,32 +6680,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>6276</t>
+          <t>7033</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>3842</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9669</t>
+          <t>11966</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>34,48%</t>
+          <t>29,78%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>53,12%</t>
+          <t>50,66%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6715,32 +6715,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>20376</t>
+          <t>27409</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>14241</t>
+          <t>19430</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>28499</t>
+          <t>37014</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>39,84%</t>
+          <t>42,14%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>29,87%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>55,72%</t>
+          <t>56,9%</t>
         </is>
       </c>
     </row>
@@ -6758,32 +6758,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4634</t>
+          <t>4671</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1320</t>
+          <t>1106</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10288</t>
+          <t>10576</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>31,23%</t>
+          <t>25,53%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6793,32 +6793,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1883</t>
+          <t>4052</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>354</t>
+          <t>1192</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5367</t>
+          <t>8452</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>35,79%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6828,32 +6828,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>6517</t>
+          <t>8724</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2611</t>
+          <t>3764</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>12136</t>
+          <t>16837</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>25,88%</t>
         </is>
       </c>
     </row>
@@ -6871,32 +6871,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>6071</t>
+          <t>7073</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2437</t>
+          <t>2561</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13922</t>
+          <t>14630</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>42,26%</t>
+          <t>35,31%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6906,32 +6906,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>5596</t>
+          <t>6748</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2776</t>
+          <t>3437</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9262</t>
+          <t>10808</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>30,74%</t>
+          <t>28,57%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>50,88%</t>
+          <t>45,76%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6941,32 +6941,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>11667</t>
+          <t>13821</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>6863</t>
+          <t>7804</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>19301</t>
+          <t>21279</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>37,74%</t>
+          <t>32,71%</t>
         </is>
       </c>
     </row>
@@ -6984,32 +6984,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2749</t>
+          <t>3549</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>714</t>
+          <t>985</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7296</t>
+          <t>8900</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7019,32 +7019,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3271</t>
+          <t>4486</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>2180</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6367</t>
+          <t>8586</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,98%</t>
+          <t>36,35%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7054,32 +7054,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>6020</t>
+          <t>8034</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2922</t>
+          <t>4159</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10744</t>
+          <t>13918</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>21,4%</t>
         </is>
       </c>
     </row>
@@ -7097,32 +7097,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>5388</t>
+          <t>5761</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1992</t>
+          <t>2155</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>12388</t>
+          <t>15182</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>37,61%</t>
+          <t>36,65%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7132,7 +7132,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1177</t>
+          <t>1300</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -7142,12 +7142,12 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3752</t>
+          <t>4096</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -7157,7 +7157,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7167,32 +7167,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>6565</t>
+          <t>7060</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2506</t>
+          <t>3126</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>13092</t>
+          <t>13832</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>21,26%</t>
         </is>
       </c>
     </row>
@@ -7210,17 +7210,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>32942</t>
+          <t>41429</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>32942</t>
+          <t>41429</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>32942</t>
+          <t>41429</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7245,17 +7245,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>18203</t>
+          <t>23619</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>18203</t>
+          <t>23619</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>18203</t>
+          <t>23619</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7280,17 +7280,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>51145</t>
+          <t>65048</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>51145</t>
+          <t>65048</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>51145</t>
+          <t>65048</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7327,32 +7327,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>89355</t>
+          <t>97779</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>25345</t>
+          <t>77376</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>183282</t>
+          <t>117640</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>33,01%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>26,12%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>35,89%</t>
+          <t>39,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7362,32 +7362,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>46089</t>
+          <t>53931</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>35868</t>
+          <t>42510</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>57146</t>
+          <t>65556</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,89%</t>
+          <t>25,71%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7397,32 +7397,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>135444</t>
+          <t>151710</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>57074</t>
+          <t>129546</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>215513</t>
+          <t>174328</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>27,52%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>23,5%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>29,11%</t>
+          <t>31,63%</t>
         </is>
       </c>
     </row>
@@ -7440,32 +7440,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>55337</t>
+          <t>63797</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13798</t>
+          <t>48701</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>116184</t>
+          <t>81994</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>27,68%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7475,32 +7475,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>37947</t>
+          <t>43857</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>29528</t>
+          <t>33903</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>49205</t>
+          <t>54888</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>21,52%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7510,32 +7510,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>93284</t>
+          <t>107655</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>42895</t>
+          <t>88381</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>149736</t>
+          <t>126821</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>23,01%</t>
         </is>
       </c>
     </row>
@@ -7553,32 +7553,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>60585</t>
+          <t>63741</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>18540</t>
+          <t>49462</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>125756</t>
+          <t>81023</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>21,52%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>27,35%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7588,32 +7588,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>61877</t>
+          <t>65334</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>49638</t>
+          <t>53244</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>74198</t>
+          <t>77716</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>25,62%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>20,88%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>32,32%</t>
+          <t>30,48%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7623,32 +7623,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>122462</t>
+          <t>129075</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>51718</t>
+          <t>110673</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>191646</t>
+          <t>151068</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>27,41%</t>
         </is>
       </c>
     </row>
@@ -7666,32 +7666,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>279117</t>
+          <t>42173</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>57061</t>
+          <t>29830</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>443611</t>
+          <t>56090</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>54,66%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>86,87%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7701,32 +7701,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>35004</t>
+          <t>39600</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>25993</t>
+          <t>29454</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>46105</t>
+          <t>51387</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>20,15%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7736,32 +7736,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>314121</t>
+          <t>81773</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>96561</t>
+          <t>67048</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>550167</t>
+          <t>100859</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>42,44%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>74,32%</t>
+          <t>18,3%</t>
         </is>
       </c>
     </row>
@@ -7779,32 +7779,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>26275</t>
+          <t>28733</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6258</t>
+          <t>18621</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>57613</t>
+          <t>47107</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7814,32 +7814,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>48641</t>
+          <t>52285</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>38158</t>
+          <t>41649</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>60826</t>
+          <t>66789</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>26,19%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7849,32 +7849,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>74916</t>
+          <t>81019</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>30865</t>
+          <t>64540</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>119896</t>
+          <t>102739</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>18,64%</t>
         </is>
       </c>
     </row>
@@ -7892,17 +7892,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>510669</t>
+          <t>296224</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>510669</t>
+          <t>296224</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>510669</t>
+          <t>296224</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7927,17 +7927,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>229558</t>
+          <t>255008</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>229558</t>
+          <t>255008</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>229558</t>
+          <t>255008</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7962,17 +7962,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>740228</t>
+          <t>551232</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>740228</t>
+          <t>551232</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>740228</t>
+          <t>551232</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8009,32 +8009,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>36434</t>
+          <t>39450</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>25026</t>
+          <t>29088</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>48063</t>
+          <t>54073</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>28,19%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>38,38%</t>
+          <t>38,64%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8044,32 +8044,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>27531</t>
+          <t>28507</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>19652</t>
+          <t>20732</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>37201</t>
+          <t>38489</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>24,74%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>35,19%</t>
+          <t>33,41%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8079,32 +8079,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>63965</t>
+          <t>67957</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>50626</t>
+          <t>54309</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>79525</t>
+          <t>85505</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>27,7%</t>
+          <t>26,63%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>34,44%</t>
+          <t>33,51%</t>
         </is>
       </c>
     </row>
@@ -8122,32 +8122,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>14879</t>
+          <t>15761</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8704</t>
+          <t>8974</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>23850</t>
+          <t>24798</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8157,32 +8157,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>13973</t>
+          <t>15362</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8650</t>
+          <t>9479</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>21610</t>
+          <t>22666</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8192,32 +8192,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>28853</t>
+          <t>31122</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>20366</t>
+          <t>22213</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>39137</t>
+          <t>42770</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>16,76%</t>
         </is>
       </c>
     </row>
@@ -8235,32 +8235,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>29545</t>
+          <t>35828</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>20414</t>
+          <t>24882</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>41484</t>
+          <t>48629</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>25,6%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>33,13%</t>
+          <t>34,75%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8270,32 +8270,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>27527</t>
+          <t>31005</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>19780</t>
+          <t>22594</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>36107</t>
+          <t>40929</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>26,04%</t>
+          <t>26,91%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>19,61%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>34,16%</t>
+          <t>35,53%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8305,32 +8305,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>57072</t>
+          <t>66833</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>45483</t>
+          <t>53500</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>69899</t>
+          <t>81743</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>26,19%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>30,27%</t>
+          <t>32,04%</t>
         </is>
       </c>
     </row>
@@ -8348,32 +8348,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>13515</t>
+          <t>13816</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7532</t>
+          <t>7312</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>21117</t>
+          <t>22922</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8383,32 +8383,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>15347</t>
+          <t>17353</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>9211</t>
+          <t>10496</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>23241</t>
+          <t>25272</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>21,94%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8418,32 +8418,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>28862</t>
+          <t>31169</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>20546</t>
+          <t>21397</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>39280</t>
+          <t>42368</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>16,61%</t>
         </is>
       </c>
     </row>
@@ -8461,32 +8461,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>30842</t>
+          <t>35087</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>20501</t>
+          <t>23637</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>44222</t>
+          <t>50541</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>25,07%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>35,32%</t>
+          <t>36,12%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8496,32 +8496,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>21322</t>
+          <t>22979</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>14577</t>
+          <t>15586</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>29120</t>
+          <t>30902</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>26,82%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8531,32 +8531,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>52164</t>
+          <t>58066</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>39207</t>
+          <t>44775</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>66586</t>
+          <t>74805</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>29,32%</t>
         </is>
       </c>
     </row>
@@ -8574,17 +8574,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>125215</t>
+          <t>139941</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>125215</t>
+          <t>139941</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>125215</t>
+          <t>139941</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -8609,17 +8609,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>105701</t>
+          <t>115206</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>105701</t>
+          <t>115206</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>105701</t>
+          <t>115206</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8644,17 +8644,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>230916</t>
+          <t>255147</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>230916</t>
+          <t>255147</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>230916</t>
+          <t>255147</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8691,32 +8691,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>139889</t>
+          <t>157604</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>51538</t>
+          <t>131897</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>229422</t>
+          <t>183907</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>33,0%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>27,62%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>34,3%</t>
+          <t>38,51%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8726,32 +8726,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>79896</t>
+          <t>89471</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>66391</t>
+          <t>75624</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>94081</t>
+          <t>107040</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>22,72%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>27,18%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8761,32 +8761,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>219785</t>
+          <t>247076</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>107022</t>
+          <t>218634</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>296113</t>
+          <t>275532</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>28,35%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>25,09%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>28,97%</t>
+          <t>31,62%</t>
         </is>
       </c>
     </row>
@@ -8804,32 +8804,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>74851</t>
+          <t>84230</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>28837</t>
+          <t>66760</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>127138</t>
+          <t>102644</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>21,49%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8839,32 +8839,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>53803</t>
+          <t>63271</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>43678</t>
+          <t>52070</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>65782</t>
+          <t>77353</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8874,32 +8874,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>128654</t>
+          <t>147501</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>58070</t>
+          <t>125919</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>177732</t>
+          <t>171831</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>19,72%</t>
         </is>
       </c>
     </row>
@@ -8917,32 +8917,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>96201</t>
+          <t>106642</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>39196</t>
+          <t>87892</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>160825</t>
+          <t>128986</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>27,01%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8952,32 +8952,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>95001</t>
+          <t>103088</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>82032</t>
+          <t>88282</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>111495</t>
+          <t>117797</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>26,88%</t>
+          <t>26,18%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>22,42%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>31,54%</t>
+          <t>29,91%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8987,32 +8987,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>191202</t>
+          <t>209729</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>89824</t>
+          <t>185288</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>260980</t>
+          <t>237023</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>24,07%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>21,26%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>27,2%</t>
         </is>
       </c>
     </row>
@@ -9030,32 +9030,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>295382</t>
+          <t>59538</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>73058</t>
+          <t>45395</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>521088</t>
+          <t>77056</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>44,16%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>77,91%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9065,32 +9065,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>53622</t>
+          <t>61438</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>42565</t>
+          <t>49776</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>66363</t>
+          <t>76098</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9100,32 +9100,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>349004</t>
+          <t>120976</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>131892</t>
+          <t>101684</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>702591</t>
+          <t>143075</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>34,14%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>68,73%</t>
+          <t>16,42%</t>
         </is>
       </c>
     </row>
@@ -9143,32 +9143,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>62505</t>
+          <t>69581</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>22321</t>
+          <t>51935</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>106199</t>
+          <t>92157</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9178,32 +9178,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>71140</t>
+          <t>76564</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>58433</t>
+          <t>62014</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>85632</t>
+          <t>91526</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9213,32 +9213,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>133645</t>
+          <t>146145</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>64167</t>
+          <t>122071</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>182902</t>
+          <t>172689</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>19,82%</t>
         </is>
       </c>
     </row>
@@ -9256,17 +9256,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>668827</t>
+          <t>477594</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>668827</t>
+          <t>477594</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>668827</t>
+          <t>477594</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -9291,17 +9291,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>353462</t>
+          <t>393833</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>353462</t>
+          <t>393833</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>353462</t>
+          <t>393833</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -9326,17 +9326,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1022289</t>
+          <t>871427</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1022289</t>
+          <t>871427</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1022289</t>
+          <t>871427</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
